--- a/WEB-INF/templateFile/KinShukkinBo.xlsx
+++ b/WEB-INF/templateFile/KinShukkinBo.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.200.3\0-546-0\勤怠管理システム\01_成果物\00_帳票テンプレート\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\Kintai\workspace\Kintai\WEB-INF\templateFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA381EE6-3DFF-4CC9-B4B2-627781C4184E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17025" windowHeight="11535"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,6 +23,9 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -354,8 +358,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -398,22 +402,14 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="BIZ UDゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF0070C0"/>
-      <name val="BIZ UDゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="BIZ UDゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -577,7 +573,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -586,40 +582,34 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -631,13 +621,19 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -943,25 +939,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BE46"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="2.625" style="1" customWidth="1"/>
-    <col min="3" max="6" width="2.125" style="1" customWidth="1"/>
-    <col min="7" max="24" width="2.625" style="1" customWidth="1"/>
-    <col min="25" max="33" width="2.125" style="1" customWidth="1"/>
+    <col min="1" max="2" width="2.59765625" style="1" customWidth="1"/>
+    <col min="3" max="6" width="2.09765625" style="1" customWidth="1"/>
+    <col min="7" max="24" width="2.59765625" style="1" customWidth="1"/>
+    <col min="25" max="33" width="2.09765625" style="1" customWidth="1"/>
     <col min="34" max="36" width="2.5" style="1" customWidth="1"/>
-    <col min="37" max="45" width="2.125" style="1" customWidth="1"/>
+    <col min="37" max="45" width="2.09765625" style="1" customWidth="1"/>
     <col min="46" max="48" width="2.5" style="1" customWidth="1"/>
-    <col min="49" max="57" width="2.125" style="1" customWidth="1"/>
+    <col min="49" max="57" width="2.09765625" style="1" customWidth="1"/>
     <col min="58" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" ht="45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:57" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="26" t="s">
         <v>28</v>
       </c>
@@ -1022,17 +1018,17 @@
       <c r="BD1" s="26"/>
       <c r="BE1" s="26"/>
     </row>
-    <row r="2" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="1:57" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
+    <row r="2" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="3" spans="1:57" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
       <c r="AT3" s="6"/>
       <c r="AU3" s="6"/>
       <c r="AV3" s="6"/>
@@ -1046,27 +1042,27 @@
       <c r="BD3" s="7"/>
       <c r="BE3" s="7"/>
     </row>
-    <row r="4" spans="1:57" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
-      <c r="S4" s="16"/>
-      <c r="T4" s="16"/>
+    <row r="4" spans="1:57" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
       <c r="AT4" s="25"/>
       <c r="AU4" s="25"/>
       <c r="AV4" s="25"/>
@@ -1080,78 +1076,78 @@
       <c r="BD4" s="25"/>
       <c r="BE4" s="25"/>
     </row>
-    <row r="5" spans="1:57" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="17" t="s">
+    <row r="5" spans="1:57" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16"/>
-      <c r="S5" s="16"/>
-      <c r="T5" s="16"/>
-      <c r="AL5" s="17" t="s">
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14"/>
+      <c r="AL5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="AM5" s="17"/>
-      <c r="AN5" s="17"/>
-      <c r="AO5" s="17"/>
-      <c r="AP5" s="15"/>
-      <c r="AQ5" s="16"/>
-      <c r="AR5" s="16"/>
-      <c r="AS5" s="16"/>
-      <c r="AT5" s="16"/>
-      <c r="AU5" s="16"/>
-      <c r="AV5" s="16"/>
-      <c r="AW5" s="16"/>
-      <c r="AX5" s="16"/>
-      <c r="AY5" s="16"/>
-      <c r="AZ5" s="16"/>
-      <c r="BA5" s="16"/>
-      <c r="BB5" s="16"/>
-      <c r="BC5" s="16"/>
-      <c r="BD5" s="16"/>
-      <c r="BE5" s="16"/>
-    </row>
-    <row r="6" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="7" spans="1:57" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="18" t="s">
+      <c r="AM5" s="15"/>
+      <c r="AN5" s="15"/>
+      <c r="AO5" s="15"/>
+      <c r="AP5" s="13"/>
+      <c r="AQ5" s="14"/>
+      <c r="AR5" s="14"/>
+      <c r="AS5" s="14"/>
+      <c r="AT5" s="14"/>
+      <c r="AU5" s="14"/>
+      <c r="AV5" s="14"/>
+      <c r="AW5" s="14"/>
+      <c r="AX5" s="14"/>
+      <c r="AY5" s="14"/>
+      <c r="AZ5" s="14"/>
+      <c r="BA5" s="14"/>
+      <c r="BB5" s="14"/>
+      <c r="BC5" s="14"/>
+      <c r="BD5" s="14"/>
+      <c r="BE5" s="14"/>
+    </row>
+    <row r="6" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="7" spans="1:57" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
       <c r="E7" s="24" t="s">
         <v>0</v>
       </c>
       <c r="F7" s="24"/>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="20" t="s">
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="K7" s="21"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="21"/>
-      <c r="O7" s="21"/>
-      <c r="P7" s="22"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
+      <c r="P7" s="20"/>
       <c r="Q7" s="28" t="s">
         <v>35</v>
       </c>
@@ -1159,137 +1155,137 @@
       <c r="S7" s="29"/>
       <c r="T7" s="29"/>
       <c r="U7" s="30"/>
-      <c r="V7" s="20" t="s">
+      <c r="V7" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="W7" s="21"/>
-      <c r="X7" s="21"/>
-      <c r="Y7" s="21"/>
-      <c r="Z7" s="21"/>
-      <c r="AA7" s="21"/>
-      <c r="AB7" s="21"/>
-      <c r="AC7" s="21"/>
-      <c r="AD7" s="21"/>
-      <c r="AE7" s="21"/>
-      <c r="AF7" s="21"/>
-      <c r="AG7" s="22"/>
-      <c r="AH7" s="20" t="s">
+      <c r="W7" s="19"/>
+      <c r="X7" s="19"/>
+      <c r="Y7" s="19"/>
+      <c r="Z7" s="19"/>
+      <c r="AA7" s="19"/>
+      <c r="AB7" s="19"/>
+      <c r="AC7" s="19"/>
+      <c r="AD7" s="19"/>
+      <c r="AE7" s="19"/>
+      <c r="AF7" s="19"/>
+      <c r="AG7" s="20"/>
+      <c r="AH7" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="AI7" s="21"/>
-      <c r="AJ7" s="21"/>
-      <c r="AK7" s="21"/>
-      <c r="AL7" s="21"/>
-      <c r="AM7" s="21"/>
-      <c r="AN7" s="21"/>
-      <c r="AO7" s="21"/>
-      <c r="AP7" s="21"/>
-      <c r="AQ7" s="21"/>
-      <c r="AR7" s="21"/>
-      <c r="AS7" s="22"/>
-      <c r="AT7" s="20" t="s">
+      <c r="AI7" s="19"/>
+      <c r="AJ7" s="19"/>
+      <c r="AK7" s="19"/>
+      <c r="AL7" s="19"/>
+      <c r="AM7" s="19"/>
+      <c r="AN7" s="19"/>
+      <c r="AO7" s="19"/>
+      <c r="AP7" s="19"/>
+      <c r="AQ7" s="19"/>
+      <c r="AR7" s="19"/>
+      <c r="AS7" s="20"/>
+      <c r="AT7" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="AU7" s="21"/>
-      <c r="AV7" s="21"/>
-      <c r="AW7" s="21"/>
-      <c r="AX7" s="21"/>
-      <c r="AY7" s="21"/>
-      <c r="AZ7" s="21"/>
-      <c r="BA7" s="21"/>
-      <c r="BB7" s="21"/>
-      <c r="BC7" s="21"/>
-      <c r="BD7" s="21"/>
-      <c r="BE7" s="22"/>
-    </row>
-    <row r="8" spans="1:57" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
+      <c r="AU7" s="19"/>
+      <c r="AV7" s="19"/>
+      <c r="AW7" s="19"/>
+      <c r="AX7" s="19"/>
+      <c r="AY7" s="19"/>
+      <c r="AZ7" s="19"/>
+      <c r="BA7" s="19"/>
+      <c r="BB7" s="19"/>
+      <c r="BC7" s="19"/>
+      <c r="BD7" s="19"/>
+      <c r="BE7" s="20"/>
+    </row>
+    <row r="8" spans="1:57" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
       <c r="E8" s="24"/>
       <c r="F8" s="24"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="20" t="s">
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="K8" s="21"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="21"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="20" t="s">
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="P8" s="22"/>
+      <c r="P8" s="20"/>
       <c r="Q8" s="31"/>
       <c r="R8" s="32"/>
       <c r="S8" s="32"/>
       <c r="T8" s="32"/>
       <c r="U8" s="33"/>
-      <c r="V8" s="20" t="s">
+      <c r="V8" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="W8" s="21"/>
-      <c r="X8" s="22"/>
-      <c r="Y8" s="18" t="s">
+      <c r="W8" s="19"/>
+      <c r="X8" s="20"/>
+      <c r="Y8" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="Z8" s="18"/>
-      <c r="AA8" s="18"/>
-      <c r="AB8" s="18" t="s">
+      <c r="Z8" s="16"/>
+      <c r="AA8" s="16"/>
+      <c r="AB8" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="AC8" s="18"/>
-      <c r="AD8" s="18"/>
-      <c r="AE8" s="18" t="s">
+      <c r="AC8" s="16"/>
+      <c r="AD8" s="16"/>
+      <c r="AE8" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="AF8" s="18"/>
-      <c r="AG8" s="18"/>
-      <c r="AH8" s="20" t="s">
+      <c r="AF8" s="16"/>
+      <c r="AG8" s="16"/>
+      <c r="AH8" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="AI8" s="21"/>
-      <c r="AJ8" s="22"/>
-      <c r="AK8" s="18" t="s">
+      <c r="AI8" s="19"/>
+      <c r="AJ8" s="20"/>
+      <c r="AK8" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="AL8" s="18"/>
-      <c r="AM8" s="18"/>
-      <c r="AN8" s="18" t="s">
+      <c r="AL8" s="16"/>
+      <c r="AM8" s="16"/>
+      <c r="AN8" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="AO8" s="18"/>
-      <c r="AP8" s="18"/>
-      <c r="AQ8" s="18" t="s">
+      <c r="AO8" s="16"/>
+      <c r="AP8" s="16"/>
+      <c r="AQ8" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="AR8" s="18"/>
-      <c r="AS8" s="18"/>
-      <c r="AT8" s="20" t="s">
+      <c r="AR8" s="16"/>
+      <c r="AS8" s="16"/>
+      <c r="AT8" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="AU8" s="21"/>
-      <c r="AV8" s="22"/>
-      <c r="AW8" s="18" t="s">
+      <c r="AU8" s="19"/>
+      <c r="AV8" s="20"/>
+      <c r="AW8" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="AX8" s="18"/>
-      <c r="AY8" s="18"/>
-      <c r="AZ8" s="18" t="s">
+      <c r="AX8" s="16"/>
+      <c r="AY8" s="16"/>
+      <c r="AZ8" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="BA8" s="18"/>
-      <c r="BB8" s="18"/>
-      <c r="BC8" s="18" t="s">
+      <c r="BA8" s="16"/>
+      <c r="BB8" s="16"/>
+      <c r="BC8" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="BD8" s="18"/>
-      <c r="BE8" s="18"/>
-    </row>
-    <row r="9" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="BD8" s="16"/>
+      <c r="BE8" s="16"/>
+    </row>
+    <row r="9" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="8"/>
@@ -1314,13 +1310,13 @@
       <c r="V9" s="9"/>
       <c r="W9" s="10"/>
       <c r="X9" s="11"/>
-      <c r="Y9" s="14"/>
+      <c r="Y9" s="12"/>
       <c r="Z9" s="8"/>
       <c r="AA9" s="8"/>
-      <c r="AB9" s="23"/>
+      <c r="AB9" s="21"/>
       <c r="AC9" s="8"/>
       <c r="AD9" s="8"/>
-      <c r="AE9" s="19"/>
+      <c r="AE9" s="17"/>
       <c r="AF9" s="8"/>
       <c r="AG9" s="8"/>
       <c r="AH9" s="9"/>
@@ -1348,7 +1344,7 @@
       <c r="BD9" s="8"/>
       <c r="BE9" s="8"/>
     </row>
-    <row r="10" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="8"/>
@@ -1373,13 +1369,13 @@
       <c r="V10" s="9"/>
       <c r="W10" s="10"/>
       <c r="X10" s="11"/>
-      <c r="Y10" s="14"/>
+      <c r="Y10" s="12"/>
       <c r="Z10" s="8"/>
       <c r="AA10" s="8"/>
-      <c r="AB10" s="23"/>
+      <c r="AB10" s="21"/>
       <c r="AC10" s="8"/>
       <c r="AD10" s="8"/>
-      <c r="AE10" s="19"/>
+      <c r="AE10" s="17"/>
       <c r="AF10" s="8"/>
       <c r="AG10" s="8"/>
       <c r="AH10" s="9"/>
@@ -1407,13 +1403,13 @@
       <c r="BD10" s="8"/>
       <c r="BE10" s="8"/>
     </row>
-    <row r="11" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="11"/>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
@@ -1432,50 +1428,50 @@
       <c r="V11" s="9"/>
       <c r="W11" s="10"/>
       <c r="X11" s="11"/>
-      <c r="Y11" s="14"/>
+      <c r="Y11" s="12"/>
       <c r="Z11" s="8"/>
       <c r="AA11" s="8"/>
-      <c r="AB11" s="23"/>
+      <c r="AB11" s="21"/>
       <c r="AC11" s="8"/>
       <c r="AD11" s="8"/>
-      <c r="AE11" s="19"/>
+      <c r="AE11" s="17"/>
       <c r="AF11" s="8"/>
       <c r="AG11" s="8"/>
       <c r="AH11" s="9"/>
       <c r="AI11" s="10"/>
       <c r="AJ11" s="11"/>
-      <c r="AK11" s="23"/>
+      <c r="AK11" s="21"/>
       <c r="AL11" s="8"/>
       <c r="AM11" s="8"/>
-      <c r="AN11" s="23"/>
+      <c r="AN11" s="21"/>
       <c r="AO11" s="8"/>
       <c r="AP11" s="8"/>
-      <c r="AQ11" s="19"/>
-      <c r="AR11" s="19"/>
-      <c r="AS11" s="19"/>
+      <c r="AQ11" s="17"/>
+      <c r="AR11" s="17"/>
+      <c r="AS11" s="17"/>
       <c r="AT11" s="9"/>
       <c r="AU11" s="10"/>
       <c r="AV11" s="11"/>
-      <c r="AW11" s="23"/>
+      <c r="AW11" s="21"/>
       <c r="AX11" s="8"/>
       <c r="AY11" s="8"/>
-      <c r="AZ11" s="23"/>
+      <c r="AZ11" s="21"/>
       <c r="BA11" s="8"/>
       <c r="BB11" s="8"/>
-      <c r="BC11" s="19"/>
-      <c r="BD11" s="19"/>
-      <c r="BE11" s="19"/>
-    </row>
-    <row r="12" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="BC11" s="17"/>
+      <c r="BD11" s="17"/>
+      <c r="BE11" s="17"/>
+    </row>
+    <row r="12" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
@@ -1525,16 +1521,16 @@
       <c r="BD12" s="8"/>
       <c r="BE12" s="8"/>
     </row>
-    <row r="13" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
@@ -1550,50 +1546,50 @@
       <c r="V13" s="9"/>
       <c r="W13" s="10"/>
       <c r="X13" s="11"/>
-      <c r="Y13" s="14"/>
+      <c r="Y13" s="12"/>
       <c r="Z13" s="8"/>
       <c r="AA13" s="8"/>
-      <c r="AB13" s="23"/>
+      <c r="AB13" s="21"/>
       <c r="AC13" s="8"/>
       <c r="AD13" s="8"/>
-      <c r="AE13" s="19"/>
+      <c r="AE13" s="17"/>
       <c r="AF13" s="8"/>
       <c r="AG13" s="8"/>
       <c r="AH13" s="9"/>
       <c r="AI13" s="10"/>
       <c r="AJ13" s="11"/>
-      <c r="AK13" s="23"/>
+      <c r="AK13" s="21"/>
       <c r="AL13" s="8"/>
       <c r="AM13" s="8"/>
-      <c r="AN13" s="23"/>
+      <c r="AN13" s="21"/>
       <c r="AO13" s="8"/>
       <c r="AP13" s="8"/>
-      <c r="AQ13" s="19"/>
-      <c r="AR13" s="19"/>
-      <c r="AS13" s="19"/>
+      <c r="AQ13" s="17"/>
+      <c r="AR13" s="17"/>
+      <c r="AS13" s="17"/>
       <c r="AT13" s="9"/>
       <c r="AU13" s="10"/>
       <c r="AV13" s="11"/>
-      <c r="AW13" s="23"/>
+      <c r="AW13" s="21"/>
       <c r="AX13" s="8"/>
       <c r="AY13" s="8"/>
-      <c r="AZ13" s="23"/>
+      <c r="AZ13" s="21"/>
       <c r="BA13" s="8"/>
       <c r="BB13" s="8"/>
-      <c r="BC13" s="19"/>
-      <c r="BD13" s="19"/>
-      <c r="BE13" s="19"/>
-    </row>
-    <row r="14" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="BC13" s="17"/>
+      <c r="BD13" s="17"/>
+      <c r="BE13" s="17"/>
+    </row>
+    <row r="14" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -1643,7 +1639,7 @@
       <c r="BD14" s="8"/>
       <c r="BE14" s="8"/>
     </row>
-    <row r="15" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="8"/>
@@ -1668,41 +1664,41 @@
       <c r="V15" s="9"/>
       <c r="W15" s="10"/>
       <c r="X15" s="11"/>
-      <c r="Y15" s="14"/>
+      <c r="Y15" s="12"/>
       <c r="Z15" s="8"/>
       <c r="AA15" s="8"/>
-      <c r="AB15" s="23"/>
+      <c r="AB15" s="21"/>
       <c r="AC15" s="8"/>
       <c r="AD15" s="8"/>
-      <c r="AE15" s="19"/>
+      <c r="AE15" s="17"/>
       <c r="AF15" s="8"/>
       <c r="AG15" s="8"/>
       <c r="AH15" s="9"/>
       <c r="AI15" s="10"/>
       <c r="AJ15" s="11"/>
-      <c r="AK15" s="23"/>
+      <c r="AK15" s="21"/>
       <c r="AL15" s="8"/>
       <c r="AM15" s="8"/>
-      <c r="AN15" s="23"/>
+      <c r="AN15" s="21"/>
       <c r="AO15" s="8"/>
       <c r="AP15" s="8"/>
-      <c r="AQ15" s="19"/>
-      <c r="AR15" s="19"/>
-      <c r="AS15" s="19"/>
+      <c r="AQ15" s="17"/>
+      <c r="AR15" s="17"/>
+      <c r="AS15" s="17"/>
       <c r="AT15" s="9"/>
       <c r="AU15" s="10"/>
       <c r="AV15" s="11"/>
-      <c r="AW15" s="23"/>
+      <c r="AW15" s="21"/>
       <c r="AX15" s="8"/>
       <c r="AY15" s="8"/>
-      <c r="AZ15" s="23"/>
+      <c r="AZ15" s="21"/>
       <c r="BA15" s="8"/>
       <c r="BB15" s="8"/>
-      <c r="BC15" s="19"/>
-      <c r="BD15" s="19"/>
-      <c r="BE15" s="19"/>
-    </row>
-    <row r="16" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="BC15" s="17"/>
+      <c r="BD15" s="17"/>
+      <c r="BE15" s="17"/>
+    </row>
+    <row r="16" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="8"/>
@@ -1761,7 +1757,7 @@
       <c r="BD16" s="8"/>
       <c r="BE16" s="8"/>
     </row>
-    <row r="17" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="8"/>
@@ -1820,7 +1816,7 @@
       <c r="BD17" s="8"/>
       <c r="BE17" s="8"/>
     </row>
-    <row r="18" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="8"/>
@@ -1879,16 +1875,16 @@
       <c r="BD18" s="8"/>
       <c r="BE18" s="8"/>
     </row>
-    <row r="19" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
@@ -1938,16 +1934,16 @@
       <c r="BD19" s="8"/>
       <c r="BE19" s="8"/>
     </row>
-    <row r="20" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
@@ -1997,7 +1993,7 @@
       <c r="BD20" s="8"/>
       <c r="BE20" s="8"/>
     </row>
-    <row r="21" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="8"/>
@@ -2056,7 +2052,7 @@
       <c r="BD21" s="8"/>
       <c r="BE21" s="8"/>
     </row>
-    <row r="22" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="8"/>
@@ -2115,7 +2111,7 @@
       <c r="BD22" s="8"/>
       <c r="BE22" s="8"/>
     </row>
-    <row r="23" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="8"/>
@@ -2174,7 +2170,7 @@
       <c r="BD23" s="8"/>
       <c r="BE23" s="8"/>
     </row>
-    <row r="24" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="8"/>
@@ -2233,7 +2229,7 @@
       <c r="BD24" s="8"/>
       <c r="BE24" s="8"/>
     </row>
-    <row r="25" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="8"/>
@@ -2292,16 +2288,16 @@
       <c r="BD25" s="8"/>
       <c r="BE25" s="8"/>
     </row>
-    <row r="26" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
@@ -2351,16 +2347,16 @@
       <c r="BD26" s="8"/>
       <c r="BE26" s="8"/>
     </row>
-    <row r="27" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
@@ -2410,7 +2406,7 @@
       <c r="BD27" s="8"/>
       <c r="BE27" s="8"/>
     </row>
-    <row r="28" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="8"/>
@@ -2469,7 +2465,7 @@
       <c r="BD28" s="8"/>
       <c r="BE28" s="8"/>
     </row>
-    <row r="29" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="8"/>
@@ -2528,7 +2524,7 @@
       <c r="BD29" s="8"/>
       <c r="BE29" s="8"/>
     </row>
-    <row r="30" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="8"/>
@@ -2587,7 +2583,7 @@
       <c r="BD30" s="8"/>
       <c r="BE30" s="8"/>
     </row>
-    <row r="31" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="8"/>
@@ -2646,7 +2642,7 @@
       <c r="BD31" s="8"/>
       <c r="BE31" s="8"/>
     </row>
-    <row r="32" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="8"/>
@@ -2705,16 +2701,16 @@
       <c r="BD32" s="8"/>
       <c r="BE32" s="8"/>
     </row>
-    <row r="33" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
       <c r="L33" s="8"/>
@@ -2764,16 +2760,16 @@
       <c r="BD33" s="8"/>
       <c r="BE33" s="8"/>
     </row>
-    <row r="34" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
       <c r="L34" s="8"/>
@@ -2823,7 +2819,7 @@
       <c r="BD34" s="8"/>
       <c r="BE34" s="8"/>
     </row>
-    <row r="35" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="8"/>
@@ -2882,7 +2878,7 @@
       <c r="BD35" s="8"/>
       <c r="BE35" s="8"/>
     </row>
-    <row r="36" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="8"/>
@@ -2941,7 +2937,7 @@
       <c r="BD36" s="8"/>
       <c r="BE36" s="8"/>
     </row>
-    <row r="37" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="8"/>
@@ -3000,7 +2996,7 @@
       <c r="BD37" s="8"/>
       <c r="BE37" s="8"/>
     </row>
-    <row r="38" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="8"/>
@@ -3059,7 +3055,7 @@
       <c r="BD38" s="8"/>
       <c r="BE38" s="8"/>
     </row>
-    <row r="39" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:57" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="8"/>
@@ -3118,7 +3114,7 @@
       <c r="BD39" s="8"/>
       <c r="BE39" s="8"/>
     </row>
-    <row r="40" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="3"/>
@@ -3167,235 +3163,235 @@
       <c r="AT40" s="4"/>
       <c r="AU40" s="4"/>
     </row>
-    <row r="41" spans="1:57" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="18" t="s">
+    <row r="41" spans="1:57" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="18"/>
-      <c r="I41" s="18"/>
-      <c r="J41" s="18"/>
-      <c r="K41" s="18"/>
-      <c r="L41" s="18"/>
-      <c r="M41" s="18"/>
-      <c r="N41" s="18"/>
-      <c r="O41" s="18"/>
-      <c r="P41" s="18"/>
-      <c r="Q41" s="18"/>
-      <c r="R41" s="18"/>
-      <c r="S41" s="18"/>
-      <c r="T41" s="18"/>
-      <c r="U41" s="18"/>
-      <c r="V41" s="18"/>
-      <c r="W41" s="18"/>
-      <c r="X41" s="18"/>
-      <c r="Y41" s="18"/>
-      <c r="Z41" s="18"/>
-      <c r="AA41" s="18"/>
-      <c r="AB41" s="18"/>
-      <c r="AC41" s="18"/>
-      <c r="AD41" s="18"/>
-      <c r="AE41" s="18" t="s">
+      <c r="B41" s="16"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="16"/>
+      <c r="H41" s="16"/>
+      <c r="I41" s="16"/>
+      <c r="J41" s="16"/>
+      <c r="K41" s="16"/>
+      <c r="L41" s="16"/>
+      <c r="M41" s="16"/>
+      <c r="N41" s="16"/>
+      <c r="O41" s="16"/>
+      <c r="P41" s="16"/>
+      <c r="Q41" s="16"/>
+      <c r="R41" s="16"/>
+      <c r="S41" s="16"/>
+      <c r="T41" s="16"/>
+      <c r="U41" s="16"/>
+      <c r="V41" s="16"/>
+      <c r="W41" s="16"/>
+      <c r="X41" s="16"/>
+      <c r="Y41" s="16"/>
+      <c r="Z41" s="16"/>
+      <c r="AA41" s="16"/>
+      <c r="AB41" s="16"/>
+      <c r="AC41" s="16"/>
+      <c r="AD41" s="16"/>
+      <c r="AE41" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="AF41" s="18"/>
-      <c r="AG41" s="18"/>
-      <c r="AH41" s="18"/>
-      <c r="AI41" s="18"/>
-      <c r="AJ41" s="18"/>
-      <c r="AK41" s="18"/>
-      <c r="AL41" s="18"/>
-      <c r="AM41" s="18"/>
-      <c r="AN41" s="18"/>
-      <c r="AO41" s="18"/>
-      <c r="AP41" s="18"/>
-      <c r="AQ41" s="18"/>
-      <c r="AR41" s="18"/>
-      <c r="AS41" s="18"/>
-      <c r="AT41" s="18"/>
-      <c r="AU41" s="18"/>
-      <c r="AV41" s="18" t="s">
+      <c r="AF41" s="16"/>
+      <c r="AG41" s="16"/>
+      <c r="AH41" s="16"/>
+      <c r="AI41" s="16"/>
+      <c r="AJ41" s="16"/>
+      <c r="AK41" s="16"/>
+      <c r="AL41" s="16"/>
+      <c r="AM41" s="16"/>
+      <c r="AN41" s="16"/>
+      <c r="AO41" s="16"/>
+      <c r="AP41" s="16"/>
+      <c r="AQ41" s="16"/>
+      <c r="AR41" s="16"/>
+      <c r="AS41" s="16"/>
+      <c r="AT41" s="16"/>
+      <c r="AU41" s="16"/>
+      <c r="AV41" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="AW41" s="18"/>
-      <c r="AX41" s="18"/>
-      <c r="AY41" s="18"/>
-      <c r="AZ41" s="18"/>
-      <c r="BA41" s="18"/>
-      <c r="BB41" s="18"/>
-      <c r="BC41" s="18"/>
-      <c r="BD41" s="18"/>
-      <c r="BE41" s="18"/>
-    </row>
-    <row r="42" spans="1:57" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="18" t="s">
+      <c r="AW41" s="16"/>
+      <c r="AX41" s="16"/>
+      <c r="AY41" s="16"/>
+      <c r="AZ41" s="16"/>
+      <c r="BA41" s="16"/>
+      <c r="BB41" s="16"/>
+      <c r="BC41" s="16"/>
+      <c r="BD41" s="16"/>
+      <c r="BE41" s="16"/>
+    </row>
+    <row r="42" spans="1:57" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B42" s="18"/>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18" t="s">
+      <c r="B42" s="16"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18" t="s">
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="H42" s="18"/>
-      <c r="I42" s="18"/>
-      <c r="J42" s="18" t="s">
+      <c r="H42" s="16"/>
+      <c r="I42" s="16"/>
+      <c r="J42" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="K42" s="18"/>
-      <c r="L42" s="18"/>
-      <c r="M42" s="18" t="s">
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
+      <c r="M42" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="N42" s="18"/>
-      <c r="O42" s="18"/>
-      <c r="P42" s="18" t="s">
+      <c r="N42" s="16"/>
+      <c r="O42" s="16"/>
+      <c r="P42" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="Q42" s="18"/>
-      <c r="R42" s="18"/>
-      <c r="S42" s="18" t="s">
+      <c r="Q42" s="16"/>
+      <c r="R42" s="16"/>
+      <c r="S42" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="T42" s="18"/>
-      <c r="U42" s="18"/>
-      <c r="V42" s="18" t="s">
+      <c r="T42" s="16"/>
+      <c r="U42" s="16"/>
+      <c r="V42" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="W42" s="18"/>
-      <c r="X42" s="18"/>
-      <c r="Y42" s="18" t="s">
+      <c r="W42" s="16"/>
+      <c r="X42" s="16"/>
+      <c r="Y42" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="Z42" s="18"/>
-      <c r="AA42" s="18"/>
-      <c r="AB42" s="18" t="s">
+      <c r="Z42" s="16"/>
+      <c r="AA42" s="16"/>
+      <c r="AB42" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="AC42" s="18"/>
-      <c r="AD42" s="18"/>
-      <c r="AE42" s="18" t="s">
+      <c r="AC42" s="16"/>
+      <c r="AD42" s="16"/>
+      <c r="AE42" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="AF42" s="18"/>
-      <c r="AG42" s="18"/>
-      <c r="AH42" s="18"/>
-      <c r="AI42" s="18" t="s">
+      <c r="AF42" s="16"/>
+      <c r="AG42" s="16"/>
+      <c r="AH42" s="16"/>
+      <c r="AI42" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="AJ42" s="18"/>
-      <c r="AK42" s="18"/>
-      <c r="AL42" s="18" t="s">
+      <c r="AJ42" s="16"/>
+      <c r="AK42" s="16"/>
+      <c r="AL42" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="AM42" s="18"/>
-      <c r="AN42" s="18"/>
-      <c r="AO42" s="18" t="s">
+      <c r="AM42" s="16"/>
+      <c r="AN42" s="16"/>
+      <c r="AO42" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="AP42" s="18"/>
-      <c r="AQ42" s="18"/>
-      <c r="AR42" s="18" t="s">
+      <c r="AP42" s="16"/>
+      <c r="AQ42" s="16"/>
+      <c r="AR42" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="AS42" s="18"/>
-      <c r="AT42" s="18"/>
-      <c r="AU42" s="18"/>
-      <c r="AV42" s="18" t="s">
+      <c r="AS42" s="16"/>
+      <c r="AT42" s="16"/>
+      <c r="AU42" s="16"/>
+      <c r="AV42" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="AW42" s="18"/>
-      <c r="AX42" s="18"/>
-      <c r="AY42" s="18"/>
-      <c r="AZ42" s="18"/>
-      <c r="BA42" s="18" t="s">
+      <c r="AW42" s="16"/>
+      <c r="AX42" s="16"/>
+      <c r="AY42" s="16"/>
+      <c r="AZ42" s="16"/>
+      <c r="BA42" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="BB42" s="18"/>
-      <c r="BC42" s="18"/>
-      <c r="BD42" s="18"/>
-      <c r="BE42" s="18"/>
-    </row>
-    <row r="43" spans="1:57" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="23"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-      <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="8"/>
-      <c r="M43" s="8"/>
-      <c r="N43" s="8"/>
-      <c r="O43" s="8"/>
-      <c r="P43" s="8"/>
-      <c r="Q43" s="8"/>
-      <c r="R43" s="8"/>
-      <c r="S43" s="8"/>
-      <c r="T43" s="8"/>
-      <c r="U43" s="8"/>
-      <c r="V43" s="8"/>
-      <c r="W43" s="8"/>
-      <c r="X43" s="8"/>
-      <c r="Y43" s="8"/>
-      <c r="Z43" s="8"/>
-      <c r="AA43" s="8"/>
-      <c r="AB43" s="8"/>
-      <c r="AC43" s="8"/>
-      <c r="AD43" s="8"/>
-      <c r="AE43" s="23"/>
-      <c r="AF43" s="23"/>
-      <c r="AG43" s="23"/>
-      <c r="AH43" s="23"/>
-      <c r="AI43" s="23"/>
-      <c r="AJ43" s="8"/>
-      <c r="AK43" s="8"/>
-      <c r="AL43" s="23"/>
-      <c r="AM43" s="8"/>
-      <c r="AN43" s="8"/>
-      <c r="AO43" s="23"/>
-      <c r="AP43" s="8"/>
-      <c r="AQ43" s="8"/>
-      <c r="AR43" s="23"/>
-      <c r="AS43" s="23"/>
-      <c r="AT43" s="23"/>
-      <c r="AU43" s="23"/>
-      <c r="AV43" s="8"/>
-      <c r="AW43" s="8"/>
-      <c r="AX43" s="8"/>
-      <c r="AY43" s="8"/>
-      <c r="AZ43" s="8"/>
-      <c r="BA43" s="8"/>
-      <c r="BB43" s="8"/>
-      <c r="BC43" s="8"/>
-      <c r="BD43" s="8"/>
-      <c r="BE43" s="8"/>
-    </row>
-    <row r="44" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="45" spans="1:57" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="18" t="s">
+      <c r="BB42" s="16"/>
+      <c r="BC42" s="16"/>
+      <c r="BD42" s="16"/>
+      <c r="BE42" s="16"/>
+    </row>
+    <row r="43" spans="1:57" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="22"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="23"/>
+      <c r="J43" s="23"/>
+      <c r="K43" s="23"/>
+      <c r="L43" s="23"/>
+      <c r="M43" s="23"/>
+      <c r="N43" s="23"/>
+      <c r="O43" s="23"/>
+      <c r="P43" s="23"/>
+      <c r="Q43" s="23"/>
+      <c r="R43" s="23"/>
+      <c r="S43" s="23"/>
+      <c r="T43" s="23"/>
+      <c r="U43" s="23"/>
+      <c r="V43" s="23"/>
+      <c r="W43" s="23"/>
+      <c r="X43" s="23"/>
+      <c r="Y43" s="23"/>
+      <c r="Z43" s="23"/>
+      <c r="AA43" s="23"/>
+      <c r="AB43" s="23"/>
+      <c r="AC43" s="23"/>
+      <c r="AD43" s="23"/>
+      <c r="AE43" s="22"/>
+      <c r="AF43" s="22"/>
+      <c r="AG43" s="22"/>
+      <c r="AH43" s="22"/>
+      <c r="AI43" s="22"/>
+      <c r="AJ43" s="23"/>
+      <c r="AK43" s="23"/>
+      <c r="AL43" s="22"/>
+      <c r="AM43" s="23"/>
+      <c r="AN43" s="23"/>
+      <c r="AO43" s="22"/>
+      <c r="AP43" s="23"/>
+      <c r="AQ43" s="23"/>
+      <c r="AR43" s="22"/>
+      <c r="AS43" s="22"/>
+      <c r="AT43" s="22"/>
+      <c r="AU43" s="22"/>
+      <c r="AV43" s="23"/>
+      <c r="AW43" s="23"/>
+      <c r="AX43" s="23"/>
+      <c r="AY43" s="23"/>
+      <c r="AZ43" s="23"/>
+      <c r="BA43" s="23"/>
+      <c r="BB43" s="23"/>
+      <c r="BC43" s="23"/>
+      <c r="BD43" s="23"/>
+      <c r="BE43" s="23"/>
+    </row>
+    <row r="44" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="45" spans="1:57" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B45" s="18"/>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="18"/>
-    </row>
-    <row r="46" spans="1:57" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B45" s="16"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+    </row>
+    <row r="46" spans="1:57" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="27"/>
       <c r="B46" s="27"/>
       <c r="C46" s="27"/>
@@ -3640,17 +3636,18 @@
     <mergeCell ref="AT9:AV9"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E12:F12"/>
     <mergeCell ref="A7:D8"/>
     <mergeCell ref="E7:F8"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
     <mergeCell ref="G12:I12"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="AI42:AK42"/>
     <mergeCell ref="AI43:AK43"/>
     <mergeCell ref="AL42:AN42"/>
@@ -3699,7 +3696,6 @@
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="G13:I13"/>
     <mergeCell ref="Y13:AA13"/>
-    <mergeCell ref="G11:I11"/>
     <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="AB11:AD11"/>
     <mergeCell ref="J12:N12"/>
@@ -3710,9 +3706,6 @@
     <mergeCell ref="Q13:U13"/>
     <mergeCell ref="Y10:AA10"/>
     <mergeCell ref="AB10:AD10"/>
-    <mergeCell ref="AE10:AG10"/>
-    <mergeCell ref="AK10:AM10"/>
-    <mergeCell ref="AK17:AM17"/>
     <mergeCell ref="AH15:AJ15"/>
     <mergeCell ref="AN11:AP11"/>
     <mergeCell ref="AQ11:AS11"/>
@@ -3747,6 +3740,8 @@
     <mergeCell ref="AH8:AJ8"/>
     <mergeCell ref="AH9:AJ9"/>
     <mergeCell ref="AK12:AM12"/>
+    <mergeCell ref="AE10:AG10"/>
+    <mergeCell ref="AK10:AM10"/>
     <mergeCell ref="AQ20:AS20"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="E20:F20"/>
@@ -3785,6 +3780,7 @@
     <mergeCell ref="J18:N18"/>
     <mergeCell ref="O18:P18"/>
     <mergeCell ref="Q18:U18"/>
+    <mergeCell ref="AK17:AM17"/>
     <mergeCell ref="AB21:AD21"/>
     <mergeCell ref="AE21:AG21"/>
     <mergeCell ref="AK21:AM21"/>
@@ -3998,8 +3994,6 @@
     <mergeCell ref="J36:N36"/>
     <mergeCell ref="O36:P36"/>
     <mergeCell ref="Q36:U36"/>
-    <mergeCell ref="AH37:AJ37"/>
-    <mergeCell ref="AH38:AJ38"/>
     <mergeCell ref="AB38:AD38"/>
     <mergeCell ref="AE38:AG38"/>
     <mergeCell ref="AK38:AM38"/>
@@ -4036,6 +4030,8 @@
     <mergeCell ref="G37:I37"/>
     <mergeCell ref="Y37:AA37"/>
     <mergeCell ref="V37:X37"/>
+    <mergeCell ref="AH37:AJ37"/>
+    <mergeCell ref="AH38:AJ38"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/WEB-INF/templateFile/KinShukkinBo.xlsx
+++ b/WEB-INF/templateFile/KinShukkinBo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\Kintai\workspace\Kintai\WEB-INF\templateFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA381EE6-3DFF-4CC9-B4B2-627781C4184E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC0CFCEF-C2B0-4416-ACD7-684422929507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -557,7 +557,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -659,6 +659,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1043,26 +1049,26 @@
       <c r="BE3" s="7"/>
     </row>
     <row r="4" spans="1:57" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14"/>
-      <c r="T4" s="14"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="34"/>
+      <c r="P4" s="34"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="34"/>
+      <c r="S4" s="34"/>
+      <c r="T4" s="34"/>
       <c r="AT4" s="25"/>
       <c r="AU4" s="25"/>
       <c r="AV4" s="25"/>
@@ -1109,18 +1115,18 @@
       <c r="AQ5" s="14"/>
       <c r="AR5" s="14"/>
       <c r="AS5" s="14"/>
-      <c r="AT5" s="14"/>
-      <c r="AU5" s="14"/>
-      <c r="AV5" s="14"/>
-      <c r="AW5" s="14"/>
-      <c r="AX5" s="14"/>
-      <c r="AY5" s="14"/>
-      <c r="AZ5" s="14"/>
-      <c r="BA5" s="14"/>
-      <c r="BB5" s="14"/>
-      <c r="BC5" s="14"/>
-      <c r="BD5" s="14"/>
-      <c r="BE5" s="14"/>
+      <c r="AT5" s="34"/>
+      <c r="AU5" s="34"/>
+      <c r="AV5" s="34"/>
+      <c r="AW5" s="34"/>
+      <c r="AX5" s="34"/>
+      <c r="AY5" s="34"/>
+      <c r="AZ5" s="34"/>
+      <c r="BA5" s="34"/>
+      <c r="BB5" s="34"/>
+      <c r="BC5" s="34"/>
+      <c r="BD5" s="34"/>
+      <c r="BE5" s="34"/>
     </row>
     <row r="6" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="7" spans="1:57" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -3369,16 +3375,16 @@
       <c r="AS43" s="22"/>
       <c r="AT43" s="22"/>
       <c r="AU43" s="22"/>
-      <c r="AV43" s="23"/>
-      <c r="AW43" s="23"/>
-      <c r="AX43" s="23"/>
-      <c r="AY43" s="23"/>
-      <c r="AZ43" s="23"/>
-      <c r="BA43" s="23"/>
-      <c r="BB43" s="23"/>
-      <c r="BC43" s="23"/>
-      <c r="BD43" s="23"/>
-      <c r="BE43" s="23"/>
+      <c r="AV43" s="35"/>
+      <c r="AW43" s="35"/>
+      <c r="AX43" s="35"/>
+      <c r="AY43" s="35"/>
+      <c r="AZ43" s="35"/>
+      <c r="BA43" s="35"/>
+      <c r="BB43" s="35"/>
+      <c r="BC43" s="35"/>
+      <c r="BD43" s="35"/>
+      <c r="BE43" s="35"/>
     </row>
     <row r="44" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="45" spans="1:57" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
